--- a/data/lossofsale_sg_perinthalmanna.xlsx
+++ b/data/lossofsale_sg_perinthalmanna.xlsx
@@ -3759,6 +3759,801 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>67</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">sahad</t>
+        </is>
+      </c>
+      <c r="D69" s="65">
+        <v>8891273722</v>
+      </c>
+      <c t="inlineStr" r="E69">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F69">
+        <is>
+          <t xml:space="preserve">ABDUL ADIL T P</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G69">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H69">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I69">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J69">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K69">
+        <is>
+          <t xml:space="preserve">customer liked the product black indowestern . may will update later</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>68</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">Sinan</t>
+        </is>
+      </c>
+      <c r="D70" s="65">
+        <v>9846815580</v>
+      </c>
+      <c t="inlineStr" r="E70">
+        <is>
+          <t xml:space="preserve">04-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F70">
+        <is>
+          <t xml:space="preserve">MOHAMMED SANJU K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G70">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H70">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I70">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J70">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K70">
+        <is>
+          <t xml:space="preserve">pure white iw premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>69</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">Shameer</t>
+        </is>
+      </c>
+      <c r="D71" s="65">
+        <v>7558840617</v>
+      </c>
+      <c t="inlineStr" r="E71">
+        <is>
+          <t xml:space="preserve">02-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F71">
+        <is>
+          <t xml:space="preserve">MOHAMMED SANJU K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G71">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H71">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I71">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J71">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K71">
+        <is>
+          <t xml:space="preserve">BLAZER LARGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>70</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">Afsal</t>
+        </is>
+      </c>
+      <c r="D72" s="65">
+        <v>9539860090</v>
+      </c>
+      <c t="inlineStr" r="E72">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F72">
+        <is>
+          <t xml:space="preserve">NIYAS BINU NASAR K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G72">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I72">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve">Kurtha costumer needs models not available in our store</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>71</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">adnan</t>
+        </is>
+      </c>
+      <c r="D73" s="65">
+        <v>8075091400</v>
+      </c>
+      <c t="inlineStr" r="E73">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F73">
+        <is>
+          <t xml:space="preserve">JASIMSHA K.H</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G73">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I73">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve">46blzer need</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>72</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">Ameen</t>
+        </is>
+      </c>
+      <c r="D74" s="65">
+        <v>8129971724</v>
+      </c>
+      <c t="inlineStr" r="E74">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F74">
+        <is>
+          <t xml:space="preserve">JASIMSHA K.H</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G74">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I74">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve">reviste again</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>73</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">jaseel</t>
+        </is>
+      </c>
+      <c r="D75" s="65">
+        <v>8606864311</v>
+      </c>
+      <c t="inlineStr" r="E75">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F75">
+        <is>
+          <t xml:space="preserve">ABDUL ADIL T P</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G75">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I75">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve">customer internal issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>74</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">ARUN</t>
+        </is>
+      </c>
+      <c r="D76" s="65">
+        <v>8111804907</v>
+      </c>
+      <c t="inlineStr" r="E76">
+        <is>
+          <t xml:space="preserve">04-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F76">
+        <is>
+          <t xml:space="preserve">FAHIS A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G76">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H76">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I76">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J76">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K76">
+        <is>
+          <t xml:space="preserve">WILL COME FOR DAPPRSQUAD BLACK KURTHA 28/DEC CONFIRM SIZE.TOTEL 15 QTY BUT SIZE IS NOT IDEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>75</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">roshan</t>
+        </is>
+      </c>
+      <c r="D77" s="65">
+        <v>9876543210</v>
+      </c>
+      <c t="inlineStr" r="E77">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F77">
+        <is>
+          <t xml:space="preserve">HEMANTH K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G77">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H77">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I77">
+        <is>
+          <t xml:space="preserve">SHOE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J77">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K77">
+        <is>
+          <t xml:space="preserve">FOR RENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65">
+        <v>76</v>
+      </c>
+      <c t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">Jayesh</t>
+        </is>
+      </c>
+      <c r="D78" s="65">
+        <v>9048006787</v>
+      </c>
+      <c t="inlineStr" r="E78">
+        <is>
+          <t xml:space="preserve">14-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F78">
+        <is>
+          <t xml:space="preserve">NIYAS BINU NASAR K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G78">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H78">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I78">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J78">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K78">
+        <is>
+          <t xml:space="preserve">Comfirmation soon</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65">
+        <v>77</v>
+      </c>
+      <c t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">rahees</t>
+        </is>
+      </c>
+      <c r="D79" s="65">
+        <v>9895053567</v>
+      </c>
+      <c t="inlineStr" r="E79">
+        <is>
+          <t xml:space="preserve">11-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F79">
+        <is>
+          <t xml:space="preserve">ABDUL ADIL T P</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G79">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H79">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I79">
+        <is>
+          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J79">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K79">
+        <is>
+          <t xml:space="preserve">customer need white plain texido and black belt model . not available at the store .</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65">
+        <v>78</v>
+      </c>
+      <c t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">NILL</t>
+        </is>
+      </c>
+      <c r="D80" s="65">
+        <v>9744408293</v>
+      </c>
+      <c t="inlineStr" r="E80">
+        <is>
+          <t xml:space="preserve">17-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F80">
+        <is>
+          <t xml:space="preserve">JASIMSHA K.H</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G80">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H80">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I80">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J80">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K80">
+        <is>
+          <t xml:space="preserve">ONLY FOR  ENQUIRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65">
+        <v>79</v>
+      </c>
+      <c t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">ALEN</t>
+        </is>
+      </c>
+      <c r="D81" s="65">
+        <v>7356370841</v>
+      </c>
+      <c t="inlineStr" r="E81">
+        <is>
+          <t xml:space="preserve">13-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F81">
+        <is>
+          <t xml:space="preserve">ABDUL ADIL T P</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G81">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H81">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I81">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J81">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K81">
+        <is>
+          <t xml:space="preserve">AVAILABILITY CHECKING OUR OTHER STORE  . TOTEL 5 QTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65">
+        <v>80</v>
+      </c>
+      <c t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">ANAS</t>
+        </is>
+      </c>
+      <c r="D82" s="65">
+        <v>8592083488</v>
+      </c>
+      <c t="inlineStr" r="E82">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F82">
+        <is>
+          <t xml:space="preserve">NIYAS BINU NASAR K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G82">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H82">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I82">
+        <is>
+          <t xml:space="preserve">Product Already Booked</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J82">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K82">
+        <is>
+          <t xml:space="preserve">BLACK BOTH TYPE BENGALA  BOOKED SO CUSTOMER WILL COME 30.12.2025 AFTER  ALL PRODUCT RETRUN BY CUSTOMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65">
+        <v>81</v>
+      </c>
+      <c t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">nishan</t>
+        </is>
+      </c>
+      <c r="D83" s="65">
+        <v>8714825247</v>
+      </c>
+      <c t="inlineStr" r="E83">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F83">
+        <is>
+          <t xml:space="preserve">Shahil shan v</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G83">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H83">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I83">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J83">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K83">
+        <is>
+          <t xml:space="preserve">green one side embro suite</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
